--- a/reports/member_funnel/downloads/member_funnel_7d_target_repeat_buyer.xlsx
+++ b/reports/member_funnel/downloads/member_funnel_7d_target_repeat_buyer.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F227"/>
+  <dimension ref="A1:F224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -569,7 +569,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -591,27 +591,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>veritaskm</t>
+          <t>kk_2905067716</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>01084555847</t>
+          <t>01099172715</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EDM_0220</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Saudan Pro 3L Shell</t>
+          <t>Paracutie II Windbreaker</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -623,91 +623,91 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>kk_2905067716</t>
+          <t>kk_4840543810</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>01099172715</t>
+          <t>01076561839</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Paracutie II Windbreaker</t>
+          <t>THRIVE™ REVIVE SHANDAL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>VIP_EXCLUSIVE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>przemysl</t>
+          <t>kk_4201213646</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>01031646842</t>
+          <t>01027969918</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>EDM_ECOM_cart_sale</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HAZY JOURNEY™ II WATERPROOF</t>
+          <t>Cove Beach Pant</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>VIP_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>kk_4339471474</t>
+          <t>kk_4837269061</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>01037475394</t>
+          <t>01071602672</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
+          <t>KONOS SPEED TRAIL ATR</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -719,27 +719,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>bia5408</t>
+          <t>przemysl</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>01037225787</t>
+          <t>01031646842</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PEAKFREAK RUSH™ MID OUTDRY™</t>
+          <t>HAZY JOURNEY™ II WATERPROOF</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -751,27 +751,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>kk_4546862086</t>
+          <t>kk_4339471474</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>01067901783</t>
+          <t>01037475394</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Silver Ridge Elite Convertible Pant</t>
+          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -783,12 +783,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>kk_4201213646</t>
+          <t>kk_3632271089</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>01027969918</t>
+          <t>01035264297</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EDM_ECOM_cart_sale</t>
+          <t>KAKAO_CH_MESSAGE_0226_BTS</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cove Beach Pant</t>
+          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -815,27 +815,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>shyguy0105</t>
+          <t>bia5408</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>01038050293</t>
+          <t>01037225787</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0209_NEWYEAR</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Arctic Crest Bonded Full Zip</t>
+          <t>PEAKFREAK RUSH™ MID OUTDRY™</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -847,27 +847,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>kk_4823936009</t>
+          <t>kk_4546862086</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>01089393759</t>
+          <t>01067901783</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Castle Rock 20L Backpack II</t>
+          <t>Silver Ridge Elite Convertible Pant</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -879,12 +879,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>kk_4581508260</t>
+          <t>shyguy0105</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>01089654012</t>
+          <t>01038050293</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_MENU_0209_NEWYEAR</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CRESTWOOD™ MID WATERPROOF WIDE</t>
+          <t>Arctic Crest Bonded Full Zip</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -911,27 +911,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>jjjino</t>
+          <t>kk_4823936009</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>01053807866</t>
+          <t>01089393759</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EDM_0202_newyear_ver1</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tumu Heights™ Jacket</t>
+          <t>Castle Rock 20L Backpack II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -943,12 +943,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>firstbaek</t>
+          <t>sunnyway21</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>01042145317</t>
+          <t>01021890517</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -958,12 +958,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>TRANS TREKKER™ OUTDRY™ WIDE</t>
+          <t>Triple Canyon 24L Backpack</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -975,27 +975,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>siwago</t>
+          <t>kk_4581508260</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>01033066627</t>
+          <t>01089654012</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arctic Crest Bonded Full Zip</t>
+          <t>CRESTWOOD™ MID WATERPROOF WIDE</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1007,12 +1007,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>my8532185</t>
+          <t>jjjino</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>01029602185</t>
+          <t>01053807866</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>KAKAO_FridnsTalk_CartSale</t>
+          <t>EDM_0202_newyear_ver1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>W's Hollowtop Mountain 2L Jacket</t>
+          <t>Tumu Heights™ Jacket</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1039,12 +1039,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>zzzing2sj</t>
+          <t>firstbaek</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>01040825103</t>
+          <t>01042145317</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1054,12 +1054,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>JAAWAA WP</t>
+          <t>TRANS TREKKER™ OUTDRY™ WIDE</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1071,27 +1071,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>senggun</t>
+          <t>siwago</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>01053217050</t>
+          <t>01033066627</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Silver Ridge Utility Vest</t>
+          <t>Arctic Crest Bonded Full Zip</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1103,12 +1103,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>kk_2958892604</t>
+          <t>my8532185</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>01032407670</t>
+          <t>01029602185</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_FridnsTalk_CartSale</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
+          <t>W's Hollowtop Mountain 2L Jacket</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1135,27 +1135,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>kk_4229942652</t>
+          <t>zzzing2sj</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>01074586556</t>
+          <t>01040825103</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>M's Dart Forest Corduroy Shirts</t>
+          <t>JAAWAA WP</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1167,27 +1167,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>kk_3944538221</t>
+          <t>senggun</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>01067575525</t>
+          <t>01053217050</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Light Canyon Soft Shell Jacket</t>
+          <t>Silver Ridge Utility Vest</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1199,27 +1199,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>rkdwjd1107</t>
+          <t>umbro98sc</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>01086634156</t>
+          <t>01027941141</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Paracutie II Windbreaker</t>
+          <t>TRANS TREKKER™ OUTDRY™ WIDE</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1231,12 +1231,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>kk_4653279631</t>
+          <t>kk_2958892604</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>01048492743</t>
+          <t>01032407670</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1246,12 +1246,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>M's Jerry Cove Crew</t>
+          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1263,12 +1263,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>qwertlhy</t>
+          <t>kk_4229942652</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>01022573817</t>
+          <t>01074586556</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1278,12 +1278,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>THRIVE REVIVE SHANDAL</t>
+          <t>M's Dart Forest Corduroy Shirts</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1295,27 +1295,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>yalrud</t>
+          <t>rkdwjd1107</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>01093710427</t>
+          <t>01086634156</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>VOYAGER FLX PCT</t>
+          <t>Paracutie II Windbreaker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1327,27 +1327,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>kk_4742727612</t>
+          <t>kk_4653279631</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>01048438355</t>
+          <t>01048492743</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>[PF]A SC_상시(1865MF,구매 장바구니)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pepper Rock 23L Backpack</t>
+          <t>M's Jerry Cove Crew</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1359,12 +1359,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>kk_4811115248</t>
+          <t>qwertlhy</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>01032638676</t>
+          <t>01022573817</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1374,12 +1374,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>M's Second Peak Crew</t>
+          <t>THRIVE REVIVE SHANDAL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1391,12 +1391,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>kk_4840268400</t>
+          <t>kk_4824047142</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>01095248011</t>
+          <t>01093696318</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1406,12 +1406,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Castle Rock™ 25L Backpack II</t>
+          <t>Paracutie II Windbreaker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1423,27 +1423,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>hikehiking</t>
+          <t>henhaojin</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>01064558877</t>
+          <t>01053508016</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CRESTWOOD MID WATERPROOF WIDE</t>
+          <t>M's Current Cove Tapered Pants</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1455,27 +1455,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>kk_4305828924</t>
+          <t>yalrud</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>01052248580</t>
+          <t>01093710427</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Castle Rock™ 20L Backpack II</t>
+          <t>VOYAGER FLX PCT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1487,12 +1487,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>gamja</t>
+          <t>kk_4742727612</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>01076747777</t>
+          <t>01048438355</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ms Hike Bowl Cove™ Fleece Jacket</t>
+          <t>Pepper Rock 23L Backpack</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1519,27 +1519,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>kk_4234884689_2</t>
+          <t>kk_4811115248</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>01056418131</t>
+          <t>01032638676</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Marble Canyon™ Overlay Hoodie</t>
+          <t>M's Second Peak Crew</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1551,12 +1551,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>saramimda</t>
+          <t>hikehiking</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>01072663960</t>
+          <t>01064558877</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MONTRAIL TRINITY AG II</t>
+          <t>CRESTWOOD MID WATERPROOF WIDE</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1583,12 +1583,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>kk_4640153364</t>
+          <t>serejohn</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>01082254246</t>
+          <t>01062169182</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,논타겟)</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>PFG Unted™ Pant</t>
+          <t>[GRAFFLEX] Dash to Cove Graphic Tee</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1615,12 +1615,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>kk_3225225310</t>
+          <t>kk_4305828924</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>01032977623</t>
+          <t>01052248580</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1630,12 +1630,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Lake To Avenue Graphic Ss Tee</t>
+          <t>Castle Rock™ 20L Backpack II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1647,27 +1647,27 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>kk_4833588305</t>
+          <t>gamja</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>01029767391</t>
+          <t>01076747777</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bonre Forest 20L Packable Backpack</t>
+          <t>Ms Hike Bowl Cove™ Fleece Jacket</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>kk_4304355753</t>
+          <t>kk_4234884689_2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>01041289534</t>
+          <t>01056418131</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Crest To Valley Graphic Ss Tee</t>
+          <t>Marble Canyon™ Overlay Hoodie</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1711,27 +1711,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>iama99</t>
+          <t>kk_4640153364</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>01085853044</t>
+          <t>01082254246</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>[PF]전환_상시(2565MF,논타겟)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Speed Trail Ball Cap</t>
+          <t>PFG Unted™ Pant</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1775,12 +1775,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ounorman</t>
+          <t>kk_3225225310</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>01051592511</t>
+          <t>01032977623</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1807,12 +1807,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>boribori123</t>
+          <t>kk_4833588305</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>01033660769</t>
+          <t>01029767391</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>PEAKFREAK RUSH OUTDRY WIDE</t>
+          <t>Bonre Forest 20L Packable Backpack</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1839,12 +1839,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>c300047</t>
+          <t>kk_4304355753</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>01032881635</t>
+          <t>01041289534</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Acker Rock Twill Short</t>
+          <t>Crest To Valley Graphic Ss Tee</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -1871,44 +1871,44 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>kk_3896853326</t>
+          <t>montrail</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>01039275630</t>
+          <t>01096613534</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
+          <t>PFG Unted™ Pant</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>VIP_EXCLUSIVE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>kk_4768982564</t>
+          <t>ounorman</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>01031185855</t>
+          <t>01051592511</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1918,29 +1918,29 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Acker Rock Twill Interchange Jacket</t>
+          <t>Lake To Avenue Graphic Ss Tee</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>VIP_EXCLUSIVE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>goodysjs</t>
+          <t>boribori123</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>01045171616</t>
+          <t>01033660769</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1950,29 +1950,29 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
+          <t>PEAKFREAK RUSH OUTDRY WIDE</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>VIP_EXCLUSIVE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>j5273</t>
+          <t>c300047</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>01086999637</t>
+          <t>01032881635</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1982,61 +1982,61 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>WHIPRAY WIDE</t>
+          <t>Acker Rock Twill Short</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>VIP_EXCLUSIVE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>kk_3845650101</t>
+          <t>c100224</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>01037981329</t>
+          <t>01053261660</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>KAKAO_FridnsTalk_CartSale</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Centrillium II Jacket</t>
+          <t>W Saudan Pro 3L Shell</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>VIP_EXCLUSIVE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>kk_4764383017</t>
+          <t>kk_3896853326</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>01020172867</t>
+          <t>01039275630</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2046,93 +2046,93 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Arctic Crest Down Hooded Jacket</t>
+          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>VIP_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>hunippp</t>
+          <t>kk_4768982564</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>01039176929</t>
+          <t>01031185855</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LMS_ECOM_familycoupon</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Centrillium II Jacket</t>
+          <t>Acker Rock Twill Interchange Jacket</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>VIP_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>kk_3522504125</t>
+          <t>goodysjs</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>01029777895</t>
+          <t>01045171616</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LMS_ECOM</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>W Saudan Pro 3L Shell</t>
+          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>VIP_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>sotank</t>
+          <t>j5273</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>01090171948</t>
+          <t>01086999637</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0209_EGGIPOUTCH</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bahama Elite LS Shirt</t>
+          <t>WHIPRAY WIDE</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2159,27 +2159,27 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>jjwsky7</t>
+          <t>kk_3845650101</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>01046339417</t>
+          <t>01037981329</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_FridnsTalk_CartSale</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>KONOS SPEED TRAIL ATR</t>
+          <t>Centrillium II Jacket</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2191,12 +2191,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>kk_4520354464</t>
+          <t>kk_4764383017</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>01054248386</t>
+          <t>01020172867</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2206,12 +2206,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Saudan Pro 3L Shell</t>
+          <t>Arctic Crest Down Hooded Jacket</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2223,12 +2223,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>kk_3381078385</t>
+          <t>hunippp</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>01063639993</t>
+          <t>01039176929</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2238,61 +2238,61 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>LMS_ECOM_familycoupon</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>M's 365 Mountain II Shirts Jacket</t>
+          <t>Centrillium II Jacket</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>VIP_EXCLUSIVE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>kk_4102520032</t>
+          <t>kk_3522504125</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>01054412351</t>
+          <t>01029777895</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>M's Cow Mountain 2L Jacket</t>
+          <t>W Saudan Pro 3L Shell</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>VIP_EXCLUSIVE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>kk_3528822549</t>
+          <t>sotank</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>01073553486</t>
+          <t>01090171948</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2302,44 +2302,44 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>LMS_ECOM_0209_EGGIPOUTCH</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>OutDry Extreme™ Wyldwood™ Shell</t>
+          <t>Bahama Elite LS Shirt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>VIP_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>kk_4550188281</t>
+          <t>jjwsky7</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>01035969181</t>
+          <t>01046339417</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>TRANS TRAIL WATERPROOF</t>
+          <t>KONOS SPEED TRAIL ATR</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2351,12 +2351,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>tkwogml</t>
+          <t>kk_4520354464</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>01044597006</t>
+          <t>01054248386</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2366,12 +2366,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>THRIVE REVIVE SHANDAL</t>
+          <t>Saudan Pro 3L Shell</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2383,12 +2383,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>lnk1006</t>
+          <t>kk_3381078385</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>01091777718</t>
+          <t>01063639993</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2398,12 +2398,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>VOYAGER FLX PCT</t>
+          <t>M's 365 Mountain II Shirts Jacket</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2415,59 +2415,59 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>fri304439fri</t>
+          <t>kk_4102520032</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>01088783835</t>
+          <t>01054412351</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
+          <t>M's Cow Mountain 2L Jacket</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>VIP_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>kk_4535776518</t>
+          <t>kk_3528822549</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>01036941922</t>
+          <t>01073553486</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>HAZY JOURNEY™ II WATERPROOF</t>
+          <t>OutDry Extreme™ Wyldwood™ Shell</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2479,59 +2479,59 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>kk_4743244830</t>
+          <t>kk_4550188281</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>01042380408</t>
+          <t>01035969181</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>CRESTWOOD™ MID WATERPROOF WIDE</t>
+          <t>TRANS TRAIL WATERPROOF</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>VIP_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>kk_4660996092</t>
+          <t>tkwogml</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>01027651333</t>
+          <t>01044597006</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Amaze Puff Hooded Jacket</t>
+          <t>THRIVE REVIVE SHANDAL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2543,44 +2543,44 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>kk_4235989212</t>
+          <t>lnk1006</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>01022435021</t>
+          <t>01091777718</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>365 TREK 2L Rain Jacket</t>
+          <t>VOYAGER FLX PCT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>VIP_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>kk_4438924680</t>
+          <t>kk_4535776518</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>01037945410</t>
+          <t>01036941922</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2590,12 +2590,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,논타겟)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>NEWTON WANDER WIDE</t>
+          <t>HAZY JOURNEY™ II WATERPROOF</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2607,27 +2607,27 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>pjd2000</t>
+          <t>kk_4743244830</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>01091549104</t>
+          <t>01042380408</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>KONOS TRILLIUM ATR</t>
+          <t>CRESTWOOD™ MID WATERPROOF WIDE</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2639,27 +2639,27 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>kk_4786725182</t>
+          <t>kk_4660996092</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>01044797982</t>
+          <t>01027651333</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>TRANS TREKKER™ OUTDRY™ WIDE</t>
+          <t>Amaze Puff Hooded Jacket</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2671,12 +2671,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>want1310</t>
+          <t>kk_4235989212</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>01092586122</t>
+          <t>01022435021</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2686,12 +2686,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_1024_NEW_MEN</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>M's Cow Mountain Cargo Straight Pants</t>
+          <t>365 TREK 2L Rain Jacket</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2703,27 +2703,27 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>storyfeel</t>
+          <t>pjd2000</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>01054189922</t>
+          <t>01091549104</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>EFW</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Centrillium II Jacket</t>
+          <t>KONOS TRILLIUM ATR</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2735,17 +2735,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>kk_4793407582</t>
+          <t>kk_4786725182</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>01071250169</t>
+          <t>01044797982</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2755,7 +2755,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Drop Ridge II Interchange Jacket</t>
+          <t>TRANS TREKKER™ OUTDRY™ WIDE</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2767,27 +2767,27 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>kk_3286025146</t>
+          <t>want1310</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>01037429754</t>
+          <t>01092586122</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MENU_1024_NEW_MEN</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>PEAKFREAK RUSH OUTDRY WIDE</t>
+          <t>M's Cow Mountain Cargo Straight Pants</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -2799,12 +2799,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>kk_3499397672</t>
+          <t>storyfeel</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>01036611109</t>
+          <t>01054189922</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>EFW</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Triple Canyon 24L Backpack</t>
+          <t>Centrillium II Jacket</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -2831,12 +2831,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>kk_4819770325</t>
+          <t>kk_4793407582</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>01065116877</t>
+          <t>01071250169</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>PEAKFREAK RUSH SHANDAL</t>
+          <t>Drop Ridge II Interchange Jacket</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -2863,27 +2863,27 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>kk_4815824568</t>
+          <t>kk_3286025146</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>01085407821</t>
+          <t>01037429754</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Chill Creek Cargo Pant</t>
+          <t>PEAKFREAK RUSH OUTDRY WIDE</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -2895,27 +2895,27 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>kk_4776550369</t>
+          <t>kk_3499397672</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>01085406463</t>
+          <t>01036611109</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Cove Beach Printed Vest</t>
+          <t>Triple Canyon 24L Backpack</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -2927,27 +2927,27 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>kk_3601024902</t>
+          <t>kk_4819770325</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>01031677101</t>
+          <t>01065116877</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>ROC Tech Cargo Pant</t>
+          <t>PEAKFREAK RUSH SHANDAL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -2959,27 +2959,27 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>kk_4681551954</t>
+          <t>kk_4815824568</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>01051876431</t>
+          <t>01085407821</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MESSAGE_0226_NEWARRIVAL</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Chill Creek Lightweight Pant</t>
+          <t>Chill Creek Cargo Pant</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -2991,27 +2991,27 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>sjh2219</t>
+          <t>kk_4776550369</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>01047493963</t>
+          <t>01085406463</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>EDM_0202_newyear_ver1</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Castle Rock™ 20L Backpack II</t>
+          <t>Cove Beach Printed Vest</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3023,12 +3023,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>kk_3460909635</t>
+          <t>kk_3601024902</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>01027606623</t>
+          <t>01031677101</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Crest To Valley Graphic Ss Tee</t>
+          <t>ROC Tech Cargo Pant</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3055,27 +3055,27 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>alsdo12</t>
+          <t>kk_4681551954</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>01091506559</t>
+          <t>01051876431</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MESSAGE_0226_NEWARRIVAL</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>TRANS TREKKER™ OUTDRY</t>
+          <t>Chill Creek Lightweight Pant</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3087,12 +3087,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>carg29</t>
+          <t>sjh2219</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>01026338890</t>
+          <t>01047493963</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3102,12 +3102,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>EDM_0202_newyear_ver1</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>MONTRAIL TRINITY FKT</t>
+          <t>Castle Rock™ 20L Backpack II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3119,12 +3119,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>cdrudder</t>
+          <t>kk_3460909635</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>01038885014</t>
+          <t>01027606623</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0209_NEWYEAR</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Marble Canyon™ Overlay Hoodie</t>
+          <t>Crest To Valley Graphic Ss Tee</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3151,27 +3151,27 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>kk_3889226622</t>
+          <t>alsdo12</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>01063564424</t>
+          <t>01091506559</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Silver Ridge Elite Convertible Pant</t>
+          <t>TRANS TREKKER™ OUTDRY</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3183,27 +3183,27 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>kk_3185019096</t>
+          <t>carg29</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>01041086656</t>
+          <t>01026338890</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Castle Rock 20L Backpack II</t>
+          <t>MONTRAIL TRINITY FKT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3215,12 +3215,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ks23</t>
+          <t>cdrudder</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>01041307401</t>
+          <t>01038885014</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3230,12 +3230,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>KAKAO_CH_MENU_0209_NEWYEAR</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>M Outdoor Tracks™ Vest</t>
+          <t>Marble Canyon™ Overlay Hoodie</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3247,12 +3247,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>kk_2823883875</t>
+          <t>kk_3889226622</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>01045708796</t>
+          <t>01063564424</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Sequoia Grove Printed Full Zip</t>
+          <t>Silver Ridge Elite Convertible Pant</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3279,27 +3279,27 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>julien20</t>
+          <t>kk_3185019096</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>01053585528</t>
+          <t>01041086656</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Price Stream Padded Shoulder</t>
+          <t>Castle Rock 20L Backpack II</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3311,27 +3311,27 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>rlawn15</t>
+          <t>ks23</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>01035730305</t>
+          <t>01041307401</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>365 TREK Small Bag</t>
+          <t>M Outdoor Tracks™ Vest</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3343,27 +3343,27 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>kk_4313086585</t>
+          <t>kk_2823883875</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>01088650381</t>
+          <t>01045708796</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Longhorn Ridge™ Reversible Shirt Jacket</t>
+          <t>Sequoia Grove Printed Full Zip</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3375,27 +3375,27 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>jcd7277</t>
+          <t>julien20</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>01051847278</t>
+          <t>01053585528</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Trail to Brush Booney</t>
+          <t>Price Stream Padded Shoulder</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3407,12 +3407,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>kangki79</t>
+          <t>rlawn15</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>01089137571</t>
+          <t>01035730305</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3422,12 +3422,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>CSC Heavyweight Iconic Tee</t>
+          <t>365 TREK Small Bag</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3439,27 +3439,27 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>pol30kjh</t>
+          <t>kk_4313086585</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>01089685636</t>
+          <t>01088650381</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>DriVenture Half Zip</t>
+          <t>Longhorn Ridge™ Reversible Shirt Jacket</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3471,27 +3471,27 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>sigenogoro</t>
+          <t>pol30kjh</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>01092921914</t>
+          <t>01089685636</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sunrise Strait OFZ Graphic Tee</t>
+          <t>DriVenture Half Zip</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3503,27 +3503,27 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>kk_4840135946</t>
+          <t>sigenogoro</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>01088642648</t>
+          <t>01092921914</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Lake To Avenue Graphic Ss Tee</t>
+          <t>Sunrise Strait OFZ Graphic Tee</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3535,27 +3535,27 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>colrock</t>
+          <t>kk_4840135946</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>01088177004</t>
+          <t>01088642648</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Marble Canyon™ Overlay Hoodie</t>
+          <t>Lake To Avenue Graphic Ss Tee</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3567,27 +3567,27 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>kk_2910619359</t>
+          <t>colrock</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>01032102485</t>
+          <t>01088177004</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Cass Rim™ Neck Gaiter</t>
+          <t>Marble Canyon™ Overlay Hoodie</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3599,27 +3599,27 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>kk_4655144758</t>
+          <t>kk_2910619359</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>01066615145</t>
+          <t>01032102485</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Provisions™ Ball Cap</t>
+          <t>Cass Rim™ Neck Gaiter</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3631,27 +3631,27 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>kk_4835422610</t>
+          <t>kk_4655144758</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>01028852041</t>
+          <t>01066615145</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Landroamer Scout Short</t>
+          <t>Provisions™ Ball Cap</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3663,27 +3663,27 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ipoyu</t>
+          <t>kk_4835422610</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>01089106263</t>
+          <t>01028852041</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Coolhead III Ball Cap</t>
+          <t>Landroamer Scout Short</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3695,12 +3695,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>soonjo1113</t>
+          <t>ipoyu</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>01026485655</t>
+          <t>01089106263</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Lake To Avenue Graphic Ss Tee</t>
+          <t>Coolhead III Ball Cap</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -3727,12 +3727,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>c100374</t>
+          <t>soonjo1113</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>01063328561</t>
+          <t>01026485655</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>EDM_0209_LIGHTBAG</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
+          <t>Lake To Avenue Graphic Ss Tee</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -3759,27 +3759,27 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>zxyooyxz</t>
+          <t>c100374</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>01050199077</t>
+          <t>01063328561</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>homelink</t>
+          <t>EDM_0209_LIGHTBAG</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>W's Anne Road Down Jacket</t>
+          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -3791,12 +3791,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>kk_3169816819</t>
+          <t>zxyooyxz</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>01085031001</t>
+          <t>01050199077</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3806,29 +3806,29 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>homelink</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Saudan Pro 3L Shell</t>
+          <t>W's Anne Road Down Jacket</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>VIP_EXCLUSIVE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>kk_4813527243</t>
+          <t>kk_3169816819</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01047387509</t>
+          <t>01085031001</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3838,29 +3838,29 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>365 TREK 2L Rain Jacket</t>
+          <t>Saudan Pro 3L Shell</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>VIP_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>kk_3217581241</t>
+          <t>kk_4813527243</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>01033086959</t>
+          <t>01047387509</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3870,44 +3870,44 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>KONOS SPEED TRAIL ATR</t>
+          <t>365 TREK 2L Rain Jacket</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>VIP_EXCLUSIVE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>kk_4358661540</t>
+          <t>kk_3217581241</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>01023270374</t>
+          <t>01033086959</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Cove Beach Pant</t>
+          <t>KONOS SPEED TRAIL ATR</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -3919,12 +3919,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>kk_3215602159</t>
+          <t>kk_4358661540</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>01050406700</t>
+          <t>01023270374</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3934,12 +3934,12 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>CSC1938 Dually Mountain Outerchange</t>
+          <t>Cove Beach Pant</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4239,27 +4239,27 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>kk_4819216312</t>
+          <t>kk_4837845730</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>01026733013</t>
+          <t>01020493219</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Centrillium II Jacket</t>
+          <t>Silver Ridge 3.0 LS</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4271,27 +4271,27 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>kk_4837845730</t>
+          <t>rdhujh8</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>01020493219</t>
+          <t>01020264590</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Silver Ridge 3.0 LS</t>
+          <t>18 oz SS Coffee Vacuum Bottle</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4303,27 +4303,27 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>rdhujh8</t>
+          <t>kk_4797754852</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>01020264590</t>
+          <t>01062184679</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>18 oz SS Coffee Vacuum Bottle</t>
+          <t>Acker Rock Windbreaker</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4335,27 +4335,27 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>kk_4797754852</t>
+          <t>jjlee6</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>01062184679</t>
+          <t>01094710953</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Acker Rock Windbreaker</t>
+          <t>KONOS™ TRS OUTDRY™ MID</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4367,12 +4367,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>jjlee6</t>
+          <t>hurshe2000</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>01094710953</t>
+          <t>01020775230</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>KONOS™ TRS OUTDRY™ MID</t>
+          <t>Silver Ridge Elite Convertible Pant</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4399,27 +4399,27 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>hurshe2000</t>
+          <t>sky542330</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>01020775230</t>
+          <t>01054233043</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Silver Ridge Elite Convertible Pant</t>
+          <t>PEAKFREAK RUSH MID OUTDRY</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4431,27 +4431,27 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>sky542330</t>
+          <t>truenergy</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>01054233043</t>
+          <t>01089883484</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>EDM_0311</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>PEAKFREAK RUSH MID OUTDRY</t>
+          <t>Explorer's Edge™ Insulated Jacket</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4463,27 +4463,27 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>truenergy</t>
+          <t>kk_4790165857</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>01089883484</t>
+          <t>01022541115</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>EDM_0311</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Explorer's Edge™ Insulated Jacket</t>
+          <t>Brea Falls Cotton Ripstop Pant</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4495,27 +4495,27 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>kk_4790165857</t>
+          <t>choiinsuhn</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>01022541115</t>
+          <t>01053747895</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Brea Falls Cotton Ripstop Pant</t>
+          <t>TRANS TREKKER™ OUTDRY™ WIDE</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4527,27 +4527,27 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>kk_4804345800</t>
+          <t>kk_4824291740</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>01027708361</t>
+          <t>01082630626</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Acker Rock Convertible Pant</t>
+          <t>W's Garden to Park OFZ ICE Crew</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4559,12 +4559,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>choiinsuhn</t>
+          <t>kk_3645593401</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>01053747895</t>
+          <t>01076800350</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4574,12 +4574,12 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>TRANS TREKKER™ OUTDRY™ WIDE</t>
+          <t>W's Duck River Tapered Pants</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4591,12 +4591,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>kk_4824291740</t>
+          <t>kk_4793295235</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>01082630626</t>
+          <t>01093520999</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4606,12 +4606,12 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>W's Garden to Park OFZ ICE Crew</t>
+          <t>Silver Leaf Lite Hooded Jacket</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -4623,27 +4623,27 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>kk_3645593401</t>
+          <t>sfreetimes</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>01076800350</t>
+          <t>01094213821</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>W's Duck River Tapered Pants</t>
+          <t>MONTRAIL TRINITY AG II</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -4655,27 +4655,27 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>kk_4793295235</t>
+          <t>lbw0515</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>01093520999</t>
+          <t>01026101115</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Silver Leaf Lite Hooded Jacket</t>
+          <t>W's Bays Trail Half Snap</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -4687,12 +4687,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>sfreetimes</t>
+          <t>leeji1970</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>01094213821</t>
+          <t>01090929031</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>MONTRAIL TRINITY AG II</t>
+          <t>Path Lake Bluff II Pant</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -4719,27 +4719,27 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>lbw0515</t>
+          <t>hungryeye61</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>01026101115</t>
+          <t>01090993009</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>W's Bays Trail Half Snap</t>
+          <t>M's Cow Mountain Half Zip Up</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -4751,12 +4751,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>leeji1970</t>
+          <t>xman3366</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>01090929031</t>
+          <t>01092928555</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4766,12 +4766,12 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Path Lake Bluff II Pant</t>
+          <t>THRIVE REVIVE MX BREEZE</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -4783,27 +4783,27 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>hungryeye61</t>
+          <t>shawn82</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>01090993009</t>
+          <t>01041434761</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>M's Cow Mountain Half Zip Up</t>
+          <t>Ms Hike Bowl Cove™ Fleece Jogger Pants</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -4815,27 +4815,27 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>xman3366</t>
+          <t>kk_3489983947</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>01092928555</t>
+          <t>01088058135</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>THRIVE REVIVE MX BREEZE</t>
+          <t>Helvetia II Printed Cropped Half Snap</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -4847,12 +4847,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>shawn82</t>
+          <t>jjong</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>01041434761</t>
+          <t>01026640561</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Ms Hike Bowl Cove™ Fleece Jogger Pants</t>
+          <t>Glacial Vista™ Long Sleeve Shirt</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -4879,27 +4879,27 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>kk_3489983947</t>
+          <t>kk_4801622135</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>01088058135</t>
+          <t>01062660230</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Helvetia II Printed Cropped Half Snap</t>
+          <t>Bonre Forest 20L Packable Backpack</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -4911,27 +4911,27 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>jjong</t>
+          <t>kk_4732354001</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>01026640561</t>
+          <t>01027318735</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>nap_new_members</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Glacial Vista™ Long Sleeve Shirt</t>
+          <t>Price Stream Earphone Case</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -4943,27 +4943,27 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>kk_4801622135</t>
+          <t>plk0609</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>01062660230</t>
+          <t>01027075298</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Awareness</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>benz_running_program_2026_coupon</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Bonre Forest 20L Packable Backpack</t>
+          <t>THRIVE REVIVE CLOG</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -4975,27 +4975,27 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>montrail</t>
+          <t>sahara188</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>01096613534</t>
+          <t>01029209414</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>PFG Unted™ Pant</t>
+          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5007,27 +5007,27 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>kk_4732354001</t>
+          <t>jjd2507</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>01027318735</t>
+          <t>01044449154</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>nap_new_members</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Price Stream Earphone Case</t>
+          <t>TRANS TREKKER™ OUTDRY™ WIDE</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5039,27 +5039,27 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>plk0609</t>
+          <t>pondkyl</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>01027075298</t>
+          <t>01050156619</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Awareness</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>benz_running_program_2026_coupon</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>THRIVE REVIVE CLOG</t>
+          <t>Cold Bay Dash Short Sleeve Tee</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5071,12 +5071,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>sahara188</t>
+          <t>swsga</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>01029209414</t>
+          <t>01090067664</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5091,24 +5091,24 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
+          <t>M's 365 Mountain II Shirts Jacket</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>VIP_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>jjd2507</t>
+          <t>insoule1201</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>01044449154</t>
+          <t>01024461707</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5123,24 +5123,24 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>TRANS TREKKER™ OUTDRY™ WIDE</t>
+          <t>Centrillium Jacket</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>VIP_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>pondkyl</t>
+          <t>rnjsrldn135</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>01050156619</t>
+          <t>01033756034</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5150,29 +5150,29 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Cold Bay Dash Short Sleeve Tee</t>
+          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>VIP_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>swsga</t>
+          <t>kk_4787402711</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>01090067664</t>
+          <t>01022018682</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>M's 365 Mountain II Shirts Jacket</t>
+          <t>M's Lee Hike Jacket</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5199,12 +5199,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>insoule1201</t>
+          <t>kk_3876211678</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>01024461707</t>
+          <t>01038900880</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Centrillium Jacket</t>
+          <t>Centrillium II Jacket</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5231,12 +5231,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>rnjsrldn135</t>
+          <t>siwoonp2107</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>01033756034</t>
+          <t>01031353391</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5246,29 +5246,29 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
+          <t>Arctic Crest Down Jacket</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>VIP_EXCLUSIVE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>kk_4787402711</t>
+          <t>kk_4830354827</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>01022018682</t>
+          <t>01058470790</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5278,12 +5278,12 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>M's Lee Hike Jacket</t>
+          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5295,27 +5295,27 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>kk_3876211678</t>
+          <t>likjky1207</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>01038900880</t>
+          <t>01028547812</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Centrillium II Jacket</t>
+          <t>KONOS TRILLIUM ATR</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5327,76 +5327,76 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>siwoonp2107</t>
+          <t>hee615</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>01031353391</t>
+          <t>01077099356</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Arctic Crest Down Jacket</t>
+          <t>Castle Rock 20L Backpack II</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>VIP_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>kk_4830354827</t>
+          <t>kk_4733482962</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>01058470790</t>
+          <t>01027099346</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
+          <t>TRANS TREKKER™ OUTDRY™ WIDE</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>VIP_EXCLUSIVE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>likjky1207</t>
+          <t>ckh276904</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>01028547812</t>
+          <t>01040155456</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5406,76 +5406,76 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>LMS_ECOM_0129</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>KONOS TRILLIUM ATR</t>
+          <t>Centrillium 2.5L Jacket</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>VIP_EXCLUSIVE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>hee615</t>
+          <t>kk_3184079697</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>01077099356</t>
+          <t>01051023999</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Castle Rock 20L Backpack II</t>
+          <t>Ms Hike Bowl Cove™ Fleece Jacket</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>VIP_EXCLUSIVE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>kk_4733482962</t>
+          <t>kk_4689160206</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>01027099346</t>
+          <t>01038979864</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>TRANS TREKKER™ OUTDRY™ WIDE</t>
+          <t>Ms Shotover Hill™ Insulation Jacket</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5487,27 +5487,27 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ckh276904</t>
+          <t>myulan1073</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>01040155456</t>
+          <t>01083091073</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0129</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Centrillium 2.5L Jacket</t>
+          <t>CRESTWOOD MID WATERPROOF WIDE</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5519,27 +5519,27 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>kk_3184079697</t>
+          <t>hughkang</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>01051023999</t>
+          <t>01031443232</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>[PF]A+SC_상시(1865MF,논타겟)</t>
+          <t>EDM_TOP</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Ms Hike Bowl Cove™ Fleece Jacket</t>
+          <t>CSC1938 V1 Hoodie</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -5551,27 +5551,27 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>kk_4689160206</t>
+          <t>yell1223</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>01038979864</t>
+          <t>01088381519</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>EDM_0331</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Ms Shotover Hill™ Insulation Jacket</t>
+          <t>Glacial Vista™ Long Sleeve Shirt</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -5583,12 +5583,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>myulan1073</t>
+          <t>dhtjdxor01</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>01083091073</t>
+          <t>01092953661</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>CRESTWOOD MID WATERPROOF WIDE</t>
+          <t>PEAKFREAK RUSH OUTDRY WIDE</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -5615,12 +5615,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>hughkang</t>
+          <t>kk_4368147803</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>01031443232</t>
+          <t>01047897331</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -5630,12 +5630,12 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>EDM_TOP</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>CSC1938 V1 Hoodie</t>
+          <t>Acker Rock Twill SS Button Down</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -5647,27 +5647,27 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>yell1223</t>
+          <t>jdahye17</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>01088381519</t>
+          <t>01086656630</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>EDM_0331</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Glacial Vista™ Long Sleeve Shirt</t>
+          <t>Silver Ridge Elite Pant</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -5679,27 +5679,27 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>dhtjdxor01</t>
+          <t>kk_4601143694</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>01092953661</t>
+          <t>01097179667</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>PEAKFREAK RUSH OUTDRY WIDE</t>
+          <t>M Outdoor Tracks™ Vest</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -5711,27 +5711,27 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>kk_4368147803</t>
+          <t>seven666</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>01047897331</t>
+          <t>01066979278</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>KAKAO_CH_event</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Acker Rock Twill SS Button Down</t>
+          <t>Price Stream Padded Shoulder</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -5743,12 +5743,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>jdahye17</t>
+          <t>ujung0228</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>01086656630</t>
+          <t>01080065724</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Silver Ridge Elite Pant</t>
+          <t>Quillayute Butte Ⅱ Socks</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -5775,76 +5775,76 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>kk_4601143694</t>
+          <t>rokmc8375</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>01097179667</t>
+          <t>01033942995</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>M Outdoor Tracks™ Vest</t>
+          <t>M's Tonto Dome Detachable Down Jacket</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>VIP_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>seven666</t>
+          <t>jhmun150102</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>01066979278</t>
+          <t>01029758998</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Price Stream Padded Shoulder</t>
+          <t>M's Dana Cove OFZ ICE Straight Pants</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>VIP_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ujung0228</t>
+          <t>camino</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>01080065724</t>
+          <t>01099009610</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5854,29 +5854,29 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Quillayute Butte Ⅱ Socks</t>
+          <t>W's Cow Mountain 2L Jacket</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>VIP_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>rokmc8375</t>
+          <t>kdlihms</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>01033942995</t>
+          <t>01081045474</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5891,39 +5891,39 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>M's Tonto Dome Detachable Down Jacket</t>
+          <t>M's Pinnacle to Avenue OF ICE Polo</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>VIP_EXCLUSIVE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>jhmun150102</t>
+          <t>bulls3005</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>01029758998</t>
+          <t>01030830402</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>M's Dana Cove OFZ ICE Straight Pants</t>
+          <t>KONOS TRILLIUM ATR</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -5935,12 +5935,12 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>camino</t>
+          <t>kk_4801933379</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>01099009610</t>
+          <t>01026457880</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5950,29 +5950,29 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>naversa_mo</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>W's Cow Mountain 2L Jacket</t>
+          <t>Heather Canyon II Hooded Softshell</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>VIP_EXCLUSIVE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>kdlihms</t>
+          <t>swj06cb</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>01081045474</t>
+          <t>01046805657</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>M's Pinnacle to Avenue OF ICE Polo</t>
+          <t>M's Somo Hike Vest</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -5999,12 +5999,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>bulls3005</t>
+          <t>lermont</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>01030830402</t>
+          <t>01034420435</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -6014,29 +6014,29 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>KONOS TRILLIUM ATR</t>
+          <t>Acker Rock Windbreaker</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>VIP_EXCLUSIVE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>kk_4801933379</t>
+          <t>kjhwa37</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>01026457880</t>
+          <t>01087609650</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>naversa_mo</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Heather Canyon II Hooded Softshell</t>
+          <t>Clearmont Heights Rain Jacket</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6063,27 +6063,27 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>swj06cb</t>
+          <t>sbandym</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>01046805657</t>
+          <t>01062091394</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_CH_MENU_260406_LIGHTJACKET</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>M's Somo Hike Vest</t>
+          <t>Ms Hike Bowl Cove™ Fleece Jogger Pants</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6095,12 +6095,12 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>lermont</t>
+          <t>ksk620228</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>01034420435</t>
+          <t>01032495729</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>[PF]전환_카탈로그(1865,관심사_01)</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Acker Rock Windbreaker</t>
+          <t>HAWTHORNE™ RAIN LO OMNI-TECH™</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -6127,12 +6127,12 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>kjhwa37</t>
+          <t>kk_4535859099</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>01087609650</t>
+          <t>01054285411</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6142,12 +6142,12 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Clearmont Heights Rain Jacket</t>
+          <t>Pepper Rock 23L Backpack</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -6159,27 +6159,27 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>sbandym</t>
+          <t>kk_3801410911</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>01062091394</t>
+          <t>01045293200</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_260406_LIGHTJACKET</t>
+          <t>sa</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Ms Hike Bowl Cove™ Fleece Jogger Pants</t>
+          <t>CRESTWOOD WATERPROOF WIDE</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6191,27 +6191,27 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ksk620228</t>
+          <t>kyh8632</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>01032495729</t>
+          <t>01066218632</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>HAWTHORNE™ RAIN LO OMNI-TECH™</t>
+          <t>Clearmont II Jacket</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6223,12 +6223,12 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>kk_4535859099</t>
+          <t>kk_4230443658</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>01054285411</t>
+          <t>01094668342</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Pepper Rock 23L Backpack</t>
+          <t>Clearmont II Jacket</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -6255,12 +6255,12 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>kk_3801410911</t>
+          <t>da1984</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>01045293200</t>
+          <t>01023726053</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6270,12 +6270,12 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>sa</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>CRESTWOOD WATERPROOF WIDE</t>
+          <t>CSC Outdoor Back Graphic Tee</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -6287,27 +6287,27 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>kyh8632</t>
+          <t>kk_4270375337</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>01066218632</t>
+          <t>01027026551</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Clearmont II Jacket</t>
+          <t>Speed Trail Ball Cap</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -6319,27 +6319,27 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>kk_4230443658</t>
+          <t>kk_4533242886</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>01094668342</t>
+          <t>01023738499</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Clearmont II Jacket</t>
+          <t>Landroamer Scout Pant</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -6351,27 +6351,27 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>da1984</t>
+          <t>kk_2962800060</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>01023726053</t>
+          <t>01062636809</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>[PF]전환_상시(2565MF,비구매자)</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>CSC Outdoor Back Graphic Tee</t>
+          <t>Lake To Avenue Graphic Ss Tee</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -6383,12 +6383,12 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>kk_4270375337</t>
+          <t>card4n</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>01027026551</t>
+          <t>01025192242</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6398,12 +6398,12 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_MEN</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Speed Trail Ball Cap</t>
+          <t>Trail to Brush Booney</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -6415,27 +6415,27 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>kk_4533242886</t>
+          <t>na42da</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>01023738499</t>
+          <t>01092629330</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Landroamer Scout Pant</t>
+          <t>Wallowa™ Softshell Pant</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -6447,27 +6447,27 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>kk_2962800060</t>
+          <t>ljh20050009</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>01062636809</t>
+          <t>01087079624</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>[PF]전환_상시(2565MF,비구매자)</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Lake To Avenue Graphic Ss Tee</t>
+          <t>PEAKFREAK RUSH OUTDRY WIDE</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -6479,27 +6479,27 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>card4n</t>
+          <t>kk_2928831288</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>01025192242</t>
+          <t>01055153689</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Trail to Brush Booney</t>
+          <t>18 oz SS Coffee Vacuum Bottle</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -6511,12 +6511,12 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>na42da</t>
+          <t>chun3217</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>01092629330</t>
+          <t>01058336842</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>naversa_pc</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Wallowa™ Softshell Pant</t>
+          <t>REDWOOD™35 BACKPACK</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -6543,27 +6543,27 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ljh20050009</t>
+          <t>kk_2915526863</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>01087079624</t>
+          <t>01064846310</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>PEAKFREAK RUSH OUTDRY WIDE</t>
+          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -6575,59 +6575,59 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>kk_2928831288</t>
+          <t>kk_4563468909</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>01055153689</t>
+          <t>01050047528</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>18 oz SS Coffee Vacuum Bottle</t>
+          <t>ESCAPE THRIVE TITANIUM MID OUTDRY</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>VIP_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>chun3217</t>
+          <t>photosky</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>01058336842</t>
+          <t>01045170406</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>naversa_pc</t>
+          <t>LMS_ECOM</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>REDWOOD™35 BACKPACK</t>
+          <t>KONOS TRILLIUM ATR</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -6639,27 +6639,27 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>kk_2915526863</t>
+          <t>dusdk1004</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>01064846310</t>
+          <t>01075581112</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
+          <t>W's Anne Road Down Jacket</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -6671,17 +6671,17 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>kk_4563468909</t>
+          <t>kk_4776596154</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>01050047528</t>
+          <t>01027596325</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -6691,39 +6691,39 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>ESCAPE THRIVE TITANIUM MID OUTDRY</t>
+          <t>Centrillium 2.5L Jacket</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>VIP_EXCLUSIVE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>photosky</t>
+          <t>j004073</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>01045170406</t>
+          <t>01052670610</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LMS_ECOM</t>
+          <t>Email_mkt</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>KONOS TRILLIUM ATR</t>
+          <t>Shadowcaster Zero Hoodie</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -6735,12 +6735,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>dusdk1004</t>
+          <t>kk_4818359648</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>01075581112</t>
+          <t>01065347576</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>W's Anne Road Down Jacket</t>
+          <t>CRESTWOOD MID WATERPROOF WIDE</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -6767,27 +6767,27 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>kk_4776596154</t>
+          <t>kk_4206657201</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>01027596325</t>
+          <t>01088989745</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Centrillium 2.5L Jacket</t>
+          <t>BFH Cool Tempo 2.0 Tee</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -6799,12 +6799,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>j004073</t>
+          <t>kk_4818466023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>01052670610</t>
+          <t>01071163664</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Email_mkt</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Shadowcaster Zero Hoodie</t>
+          <t>KONOS™ TRS OUTDRY™ MID</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -6831,12 +6831,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>kk_4818359648</t>
+          <t>kk_3714628976</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>01065347576</t>
+          <t>01027460780</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>CRESTWOOD MID WATERPROOF WIDE</t>
+          <t>Silver Ridge 3.0 LS</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -6863,27 +6863,27 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>kk_4206657201</t>
+          <t>erunhaha</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>01088989745</t>
+          <t>01045097410</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0211_NEW_WOMEN</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>BFH Cool Tempo 2.0 Tee</t>
+          <t>CSC Heavyweight Iconic Tee</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -6895,27 +6895,27 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>kk_4818466023</t>
+          <t>kk_4284036153</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>01071163664</t>
+          <t>01025377763</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_CH_MENU_0209_NEWYEAR</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>KONOS™ TRS OUTDRY™ MID</t>
+          <t>M's Pines Crest Dome™ Ⅱ Fleece Training Pant</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -6927,27 +6927,27 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>kk_3714628976</t>
+          <t>sakurapro</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>01027460780</t>
+          <t>01084080201</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>mail</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Silver Ridge 3.0 LS</t>
+          <t>Ms Hike Bowl Cove™ Fleece Jacket</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -6959,27 +6959,27 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>erunhaha</t>
+          <t>jas39gripen</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>01045097410</t>
+          <t>01067315967</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>(organic)</t>
+          <t>컬럼비아_DPA_240530</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>CSC Heavyweight Iconic Tee</t>
+          <t>PFG Unted™ Insulated Anorak</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -6991,12 +6991,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>kk_4284036153</t>
+          <t>kk_4643655100</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>01025377763</t>
+          <t>01062147398</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7006,12 +7006,12 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0209_NEWYEAR</t>
+          <t>KAKAO_alimtalk</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>M's Pines Crest Dome™ Ⅱ Fleece Training Pant</t>
+          <t>Pinetown Canyon Jogger</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -7023,27 +7023,27 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>sakurapro</t>
+          <t>pillaret3</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>01084080201</t>
+          <t>01028815098</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>mail</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Ms Hike Bowl Cove™ Fleece Jacket</t>
+          <t>Beach Spire Ridge IV Pant</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -7055,27 +7055,27 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>jas39gripen</t>
+          <t>itotoito</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>01067315967</t>
+          <t>01099599597</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>컬럼비아_DPA_240530</t>
+          <t>naver_brandsearch_pc</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>PFG Unted™ Insulated Anorak</t>
+          <t>Trail Traveler 28L Rucksack</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -7087,12 +7087,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>kk_4643655100</t>
+          <t>suny0596</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>01062147398</t>
+          <t>01056530596</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>KAKAO_alimtalk</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Pinetown Canyon Jogger</t>
+          <t>MONTRAIL TRINITY FKT</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -7119,12 +7119,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>pillaret3</t>
+          <t>baechang1</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>01028815098</t>
+          <t>01025462701</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7134,12 +7134,12 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Beach Spire Ridge IV Pant</t>
+          <t>Lake To Avenue Graphic Ss Tee</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -7151,27 +7151,27 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>itotoito</t>
+          <t>c100329</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>01099599597</t>
+          <t>01089002471</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>naver_brandsearch_pc</t>
+          <t>Direct</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Trail Traveler 28L Rucksack</t>
+          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -7183,27 +7183,27 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>suny0596</t>
+          <t>cjh2866</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>01056530596</t>
+          <t>01054772866</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>MONTRAIL TRINITY FKT</t>
+          <t>M's Pack Point Half Zip Up</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -7215,12 +7215,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>baechang1</t>
+          <t>bluewolf</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>01025462701</t>
+          <t>01022741671</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -7230,44 +7230,44 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Lake To Avenue Graphic Ss Tee</t>
+          <t>Silver Ridge 3.0 LS</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>VIP_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>c100329</t>
+          <t>spoon</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>01089002471</t>
+          <t>01024754504</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Direct</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>TELLURIX TITANIUM OUTDRY WIDE</t>
+          <t>KONOS™ TRS OUTDRY™ MID</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -7279,12 +7279,12 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>cjh2866</t>
+          <t>kk_4738944549</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>01054772866</t>
+          <t>01077475609</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -7299,39 +7299,39 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>M's Pack Point Half Zip Up</t>
+          <t>W’s 365 Mountain II Pants</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>GENERAL</t>
+          <t>VIP_EXCLUSIVE</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>bluewolf</t>
+          <t>nudyrody</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>01022741671</t>
+          <t>01054493261</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Silver Ridge 3.0 LS</t>
+          <t>Street Transit III Backpack</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -7343,12 +7343,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>spoon</t>
+          <t>kk_4826648232</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>01024754504</t>
+          <t>01091243804</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -7358,12 +7358,12 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>(referral)</t>
+          <t>naver_brandsearch_mobile</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>KONOS™ TRS OUTDRY™ MID</t>
+          <t>TRANS TRAIL™ WATERPROOF</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -7375,76 +7375,76 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>kk_4738944549</t>
+          <t>kk_3780813597</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>01077475609</t>
+          <t>01031519998</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>W’s 365 Mountain II Pants</t>
+          <t>ESCAPE THRIVE TITANIUM MID OUTDRY</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>VIP_EXCLUSIVE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>nudyrody</t>
+          <t>kk_3178667155</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>01054493261</t>
+          <t>01030057028</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Organic Traffic</t>
+          <t>bizboard</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Street Transit III Backpack</t>
+          <t>Acker Rock Convertible Pant</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>VIP_EXCLUSIVE</t>
+          <t>GENERAL</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>kk_4826648232</t>
+          <t>kk_4273475210</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>01091243804</t>
+          <t>01083366982</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -7454,12 +7454,12 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>naver_brandsearch_mobile</t>
+          <t>da</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>TRANS TRAIL™ WATERPROOF</t>
+          <t>VOYAGER FLX PCT</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -7471,27 +7471,27 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>kk_3780813597</t>
+          <t>kk_4523926208</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>01031519998</t>
+          <t>01028883249</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Paid Ad</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>KAKAO_CH_MENU_0212_GOODBYEWINTER</t>
+          <t>LMS_ECOM_0214_newyear</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>ESCAPE THRIVE TITANIUM MID OUTDRY</t>
+          <t>Ms Hike Bowl Cove™ Fleece Jacket</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -7503,27 +7503,27 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>kk_3178667155</t>
+          <t>eosuccess10</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>01030057028</t>
+          <t>01066916563</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Owned Channel</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>bizboard</t>
+          <t>(organic)</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Acker Rock Convertible Pant</t>
+          <t>Alder Creek Short Sleeve Tee</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -7535,27 +7535,27 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>kk_4273475210</t>
+          <t>kk_3714995686</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>01083366982</t>
+          <t>01045329255</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Owned Channel</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>da</t>
+          <t>KAKAO_CH_event</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>VOYAGER FLX PCT</t>
+          <t>Snowshoe DomeⅡ Earflap Cap</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -7567,126 +7567,30 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>kk_4523926208</t>
+          <t>kk_3814789276</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>01028883249</t>
+          <t>01038651735</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Paid Ad</t>
+          <t>Organic Traffic</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>LMS_ECOM_0214_newyear</t>
+          <t>(referral)</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Ms Hike Bowl Cove™ Fleece Jacket</t>
+          <t>Lake To Avenue Graphic Ss Tee</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>eosuccess10</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>01066916563</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>Organic Traffic</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>(organic)</t>
-        </is>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>Alder Creek Short Sleeve Tee</t>
-        </is>
-      </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>kk_3714995686</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>01045329255</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>Owned Channel</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>KAKAO_CH_event</t>
-        </is>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>Snowshoe DomeⅡ Earflap Cap</t>
-        </is>
-      </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>kk_3814789276</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>01038651735</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>Organic Traffic</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>(referral)</t>
-        </is>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>Lake To Avenue Graphic Ss Tee</t>
-        </is>
-      </c>
-      <c r="F227" t="inlineStr">
         <is>
           <t>GENERAL</t>
         </is>
